--- a/test-docs/reports/reports.xlsx
+++ b/test-docs/reports/reports.xlsx
@@ -17,6 +17,8 @@
     <sheet name="TS-Reports-Statistics" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="TS-Reports-Notifications" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="TS-Reports-Permissions" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="TS-Reports-CronNotifications" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="TS-Reports-BudgetNotifications" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'TS-Reports-CRUD'!$A$2:$J$17</definedName>
@@ -145,7 +147,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -176,6 +178,15 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1351,6 +1362,1413 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00F4B084"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="45" customWidth="1" min="3" max="3"/>
+    <col width="72" customWidth="1" min="4" max="4"/>
+    <col width="45" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="8" max="8"/>
+    <col width="26" customWidth="1" min="9" max="9"/>
+    <col width="35" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4">
+        <f>HYPERLINK("#'Plan Overview'!A1", "← Back to Plan Overview")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="14" t="inlineStr">
+        <is>
+          <t>Test ID</t>
+        </is>
+      </c>
+      <c r="B2" s="14" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="C2" s="14" t="inlineStr">
+        <is>
+          <t>Preconditions</t>
+        </is>
+      </c>
+      <c r="D2" s="14" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="E2" s="14" t="inlineStr">
+        <is>
+          <t>Expected Result</t>
+        </is>
+      </c>
+      <c r="F2" s="14" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="G2" s="14" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="H2" s="14" t="inlineStr">
+        <is>
+          <t>Requirement Ref</t>
+        </is>
+      </c>
+      <c r="I2" s="14" t="inlineStr">
+        <is>
+          <t>Module/Component</t>
+        </is>
+      </c>
+      <c r="J2" s="14" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="15" t="inlineStr">
+        <is>
+          <t>TC-RPT-101</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>Forgotten-report notification — underreported employee receives weekly email</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>Env: ttt-timemachine (clock controllable) or ttt-qa-1.
+Employee must be enabled, NOT in officeId=9 (per regression #685), and must have reported less than the weekly norm for the previous report period (taking vacations/absences into account).
+Query: SELECT e.login FROM ttt_backend.employee e JOIN ttt_backend.office o ON e.salary_office_id = o.id WHERE e.enabled = true AND o.id &lt;&gt; 9 AND NOT EXISTS (  SELECT 1 FROM ttt_backend.task_report tr   WHERE tr.executor_id = e.id   AND tr.report_date BETWEEN (current_date - INTERVAL '7 days') AND (current_date - INTERVAL '1 day')) ORDER BY random() LIMIT 1;</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>SETUP: Pick an underreported employee from the query above.
+SETUP: Clear any historical FORGOTTEN_REPORT emails via `roundcube-access --delete --subject '[QA1][TTT] Скорее всего вы забыли'` for that mailbox (or note baseline UID).
+TRIGGER: `POST /api/ttt/v1/test/reports/notify-forgotten` (empty body, requires API_SECRET_TOKEN).
+WAIT: ~60 s for EmailSendScheduler (every 20 s) to dispatch.
+VERIFY LOG: Graylog TTT-QA-1 — `message:"Report forgotten notification started"` within last 3 min (debug level).
+VERIFY LOG: Graylog TTT-QA-1 — `message:"Employees not reached reporting norm count = "` with count ≥ 1.
+EMAIL-CHECK: `roundcube-access search --since today --subject '[QA1][TTT]' --subject 'Скорее всего вы забыли зарепортиться за прошлую неделю' --to &lt;employee-email&gt;` returns ≥ 1 message.
+CLEANUP: None (idempotent email noise; next run will re-evaluate).</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>Employee's mailbox receives FORGOTTEN_REPORT email (template key `FORGOTTEN_REPORT`). Graylog shows the scheduler marker and the "Employees not reached reporting norm" count reflects the test subject employee.</t>
+        </is>
+      </c>
+      <c r="F3" s="15" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="G3" s="15" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="H3" s="6" t="inlineStr">
+        <is>
+          <t>#3423 row 1; #559</t>
+        </is>
+      </c>
+      <c r="I3" s="6" t="inlineStr">
+        <is>
+          <t>reports/cron/forgotten</t>
+        </is>
+      </c>
+      <c r="J3" s="6" t="inlineStr">
+        <is>
+          <t>Subject per email-notification-triggers §Row 1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="16" t="inlineStr">
+        <is>
+          <t>TC-RPT-102</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>Forgotten-report — employees with salary_office_id=9 (Office not assigned) excluded</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>Env: ttt-qa-1.
+At least one enabled employee with `salary_office_id = 9` who is underreported for the previous report period.
+Query: SELECT e.login FROM ttt_backend.employee e WHERE e.enabled = true AND e.salary_office_id = 9 LIMIT 1;</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>SETUP: Identify target employee with officeId=9.
+SETUP: Clear historical FORGOTTEN_REPORT emails for this mailbox.
+TRIGGER: `POST /api/ttt/v1/test/reports/notify-forgotten`.
+WAIT: 60 s.
+VERIFY LOG: Graylog shows scheduler marker fired (global — `message:"Report forgotten notification started"`).
+VERIFY LOG: Verify `"Sending notification to = "` does NOT mention this employee's login in last 5 min.
+EMAIL-CHECK: `roundcube-access search --since today --to &lt;employee-email&gt; --subject 'Скорее всего'` returns 0 messages.
+DB-CHECK: No `notification_log` insert (if applicable) for this employee in last 5 min.
+CLEANUP: None.</t>
+        </is>
+      </c>
+      <c r="E4" s="8" t="inlineStr">
+        <is>
+          <t>Even when the employee meets the underreport predicate, the office filter (officeId != 9) excludes them. Other employees may still be notified — verify the scope table via the service-level count marker.</t>
+        </is>
+      </c>
+      <c r="F4" s="16" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G4" s="16" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="H4" s="8" t="inlineStr">
+        <is>
+          <t>#3423 row 1; #685 regression</t>
+        </is>
+      </c>
+      <c r="I4" s="8" t="inlineStr">
+        <is>
+          <t>reports/cron/forgotten</t>
+        </is>
+      </c>
+      <c r="J4" s="8" t="inlineStr">
+        <is>
+          <t>#685 fix guard — 'Office not assigned' employees never get weekly reminder.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="15" t="inlineStr">
+        <is>
+          <t>TC-RPT-103</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>Forgotten-report — fully-reported employee excluded</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>Env: ttt-qa-1.
+Enabled employee with all workdays of the previous report period fully reported (effort_sum ≥ norm, ignoring vacations/sick leave).
+Query: SELECT e.login FROM ttt_backend.employee e JOIN (SELECT executor_id, SUM(effort) AS total_min   FROM ttt_backend.task_report   WHERE report_date BETWEEN (current_date - INTERVAL '7 days')   AND (current_date - INTERVAL '1 day')   GROUP BY executor_id) tr ON tr.executor_id = e.id WHERE e.enabled = true AND tr.total_min &gt;= 40 * 60 ORDER BY random() LIMIT 1;</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>SETUP: Pick a fully-reported employee.
+SETUP: Clear historical FORGOTTEN_REPORT emails for this mailbox.
+TRIGGER: `POST /api/ttt/v1/test/reports/notify-forgotten`.
+WAIT: 60 s.
+EMAIL-CHECK: `roundcube-access search --since today --to &lt;employee-email&gt; --subject 'Скорее всего'` returns 0 messages.
+VERIFY LOG: `"Sending notification to = "` does NOT mention this employee.
+CLEANUP: None.</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>Query predicate `not_reached_norm = true` filters out this employee; no email dispatched despite scheduler firing.</t>
+        </is>
+      </c>
+      <c r="F5" s="15" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G5" s="15" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="H5" s="6" t="inlineStr">
+        <is>
+          <t>#3423 row 1; #559</t>
+        </is>
+      </c>
+      <c r="I5" s="6" t="inlineStr">
+        <is>
+          <t>reports/cron/forgotten</t>
+        </is>
+      </c>
+      <c r="J5" s="6" t="inlineStr">
+        <is>
+          <t>Norm-reached negative path.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="16" t="inlineStr">
+        <is>
+          <t>TC-RPT-104</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>Forgotten-delayed notification — employee who remained underreported receives catch-up email</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>Env: ttt-timemachine (clock control recommended).
+Enabled employee who received the first FORGOTTEN_REPORT on Mon/Fri 16:00 NSK and has STILL not reported by 16:30 NSK the same day.
+Query: same base as TC-RPT-101.</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>SETUP: Pick underreported employee (query from TC-RPT-101).
+SETUP: Clear historical FORGOTTEN_REPORT emails.
+TRIGGER 1: `POST /api/ttt/v1/test/reports/notify-forgotten` (simulate the 16:00 first pass).
+WAIT: 60 s; verify one FORGOTTEN_REPORT email dispatched.
+TRIGGER 2: `POST /api/ttt/v1/test/reports/notify-forgotten-delayed` (simulate the 16:30 delayed pass).
+WAIT: 60 s.
+VERIFY LOG: Graylog — `message:"Report forgotten delayed notification started"` (debug).
+VERIFY LOG: `message:"Sending delayed notification to = "` mentions the employee.
+EMAIL-CHECK: Roundcube — employee's mailbox now shows TWO messages matching the FORGOTTEN_REPORT subject, sent ~30 min apart.
+CLEANUP: None.</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>Delayed path sends a second FORGOTTEN_REPORT email (same template, different invocation) for employees who remain underreported after the first pass.</t>
+        </is>
+      </c>
+      <c r="F6" s="16" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G6" s="16" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="H6" s="8" t="inlineStr">
+        <is>
+          <t>#3423 row 2; #559</t>
+        </is>
+      </c>
+      <c r="I6" s="8" t="inlineStr">
+        <is>
+          <t>reports/cron/forgotten-delayed</t>
+        </is>
+      </c>
+      <c r="J6" s="8" t="inlineStr">
+        <is>
+          <t>Subject predicate identical to row 1 — disambiguate via send-time (~16:30) or via log marker ‘delayed notification to ='.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="15" t="inlineStr">
+        <is>
+          <t>TC-RPT-105</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>Forgotten-delayed — employee who reported after the 16:00 pass is excluded</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>Env: ttt-timemachine.
+Employee received FORGOTTEN_REPORT at 16:00 NSK pass, then submitted reports to close the deficit before 16:30 NSK.</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>SETUP: Pick underreported employee; dispatch first FORGOTTEN_REPORT via `/notify-forgotten`.
+SETUP: Via API (as that employee) — POST missing task_reports to reach weekly norm.
+TRIGGER: `POST /api/ttt/v1/test/reports/notify-forgotten-delayed`.
+WAIT: 60 s.
+VERIFY LOG: `message:"Employee {} already reported hours for period from {} to {}"` mentions this employee.
+EMAIL-CHECK: Roundcube — only ONE FORGOTTEN_REPORT email for this employee (from the first pass), not two.
+CLEANUP: Delete the seeded task_reports if test data hygiene requires.</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>Delayed-pass skips employees whose norm gap was closed between 16:00 and 16:30 (service-level log marker `already reported` confirms the skip).</t>
+        </is>
+      </c>
+      <c r="F7" s="15" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G7" s="15" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>#3423 row 2; #559</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>reports/cron/forgotten-delayed</t>
+        </is>
+      </c>
+      <c r="J7" s="6" t="inlineStr">
+        <is>
+          <t>Negative path using the `already reported` marker as witness.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="16" t="inlineStr">
+        <is>
+          <t>TC-RPT-106</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>Reports-changed notification — manager edits employee hours → REPORT_SHEET_CHANGED email</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>Env: ttt-qa-1.
+Manager with a direct report. Manager and employee must be different users (predicate `reporter_id != executor_id`).
+Query for manager+employee pair: SELECT mgr.login AS mgr_login, emp.login AS emp_login FROM ttt_backend.employee emp JOIN ttt_backend.employee mgr ON emp.manager_id = mgr.id WHERE emp.enabled = true AND mgr.enabled = true AND mgr.login &lt;&gt; 'pvaynmaster' ORDER BY random() LIMIT 1;</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>SETUP: Resolve the (manager, employee) pair.
+SETUP: Ensure the employee has at least one task on an active project shared with the manager (join via employee_project).
+SETUP: Clear historical REPORT_SHEET_CHANGED emails for the employee.
+STEP 1: Login as MANAGER via browser.
+STEP 2: Navigate to Employees &amp; Contractors → find the subordinate.
+STEP 3: Open the weekly report sheet for YESTERDAY.
+STEP 4: Click an empty cell for an assigned task, enter 2 (hours), press Enter.
+STEP 5: Verify the cell saves with manager as reporter (reporter_id = manager.id, executor_id = employee.id).
+TRIGGER: `POST /api/ttt/v1/test/reports/notify-changed`.
+WAIT: 60 s.
+VERIFY LOG: Graylog — `message:"Start notification process"` AND `message:"Find: "` with count ≥ 1.
+EMAIL-CHECK: Roundcube — employee mailbox receives email with template data referencing the manager's name and the edited date. Subject must match the REPORT_SHEET_CHANGED predicate (captured in session 136 during first real seeding run — record the exact subject as a P2 follow-up for patterns/email-notification-triggers.md row 3).
+DB-CHECK: `SELECT reporter_id, executor_id FROM ttt_backend.task_report WHERE report_date = current_date - 1 AND reporter_id = &lt;mgr_id&gt; AND executor_id = &lt;emp_id&gt;` returns ≥ 1 row.
+CLEANUP: Via API — DELETE the manager-reported task_report rows.</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>Template `REPORT_SHEET_CHANGED` (NOT TASK_REPORT_CHANGED — per delta #1) fires for yesterday's manager-reported rows. Email arrives grouped by (manager, report_date).</t>
+        </is>
+      </c>
+      <c r="F8" s="16" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="G8" s="16" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="H8" s="8" t="inlineStr">
+        <is>
+          <t>#3423 row 3; delta #1 (template key); #570</t>
+        </is>
+      </c>
+      <c r="I8" s="8" t="inlineStr">
+        <is>
+          <t>reports/cron/changed</t>
+        </is>
+      </c>
+      <c r="J8" s="8" t="inlineStr">
+        <is>
+          <t>Delta #1 folded: template key is REPORT_SHEET_CHANGED — scope table said TASK_REPORT_CHANGED (incorrect). Predicate: reporter_id ≠ executor_id AND report_date = yesterday.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="15" t="inlineStr">
+        <is>
+          <t>TC-RPT-107</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>Reports-changed — manager edits OWN hours does NOT fire REPORT_SHEET_CHANGED</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>Env: ttt-qa-1.
+Any manager with assigned tasks (self-report scenario).
+Query: same as TC-RPT-106 mgr_login.</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>SETUP: Pick a manager.
+SETUP: Clear historical REPORT_SHEET_CHANGED emails.
+STEP 1: Login as MANAGER via browser.
+STEP 2: Navigate to My Tasks → report 2 hours for yesterday on an assigned task.
+STEP 3: Verify `reporter_id = executor_id = manager.id` in DB.
+TRIGGER: `POST /api/ttt/v1/test/reports/notify-changed`.
+WAIT: 60 s.
+VERIFY LOG: `message:"Find: 0 task reported by manager today"` (or count excludes this row).
+EMAIL-CHECK: Roundcube — no REPORT_SHEET_CHANGED email for this manager.
+DB-CHECK: No row matches `reporter_id != executor_id AND report_date = current_date - 1` from this manager's edits.
+CLEANUP: Via API — DELETE the seeded row.</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>Query predicate `reporter_id != executor_id` excludes self-reports; no email dispatched.</t>
+        </is>
+      </c>
+      <c r="F9" s="15" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G9" s="15" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>#3423 row 3</t>
+        </is>
+      </c>
+      <c r="I9" s="6" t="inlineStr">
+        <is>
+          <t>reports/cron/changed</t>
+        </is>
+      </c>
+      <c r="J9" s="6" t="inlineStr">
+        <is>
+          <t>Negative path — executor-equals-reporter filter.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="16" t="inlineStr">
+        <is>
+          <t>TC-RPT-108</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>Reports-changed — idempotency on repeated trigger within the same day</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>Env: ttt-qa-1.
+Pre-state: TC-RPT-106 ran today and dispatched a REPORT_SHEET_CHANGED email.</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>SETUP: Capture baseline email count for the affected employee (`roundcube-access count --since today --to &lt;emp-email&gt; --subject 'REPORT_SHEET_CHANGED-subject'`).
+TRIGGER 1: `POST /api/ttt/v1/test/reports/notify-changed` (within 5–10 min of the TC-RPT-106 run).
+WAIT: 60 s.
+TRIGGER 2: `POST /api/ttt/v1/test/reports/notify-changed` (second invocation).
+WAIT: 60 s.
+VERIFY LOG: Both invocations log `Start notification process`; `Find: N` count is the SAME on both runs (the service re-selects yesterday's rows every time).
+EMAIL-CHECK: Roundcube — post-trigger email count equals baseline + N (where N = rows found first time). Second trigger does NOT add emails UNLESS new manager-reported rows landed in between.
+CLEANUP: None.</t>
+        </is>
+      </c>
+      <c r="E10" s="8" t="inlineStr">
+        <is>
+          <t>Current code sends on EVERY invocation — idempotency is enforced by an `already_notified` DB flag on task_report (if present) or by the 5-minute scheduler cadence, not by the test endpoint. Document observed behavior; file a design-issue note if duplicates appear.</t>
+        </is>
+      </c>
+      <c r="F10" s="16" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G10" s="16" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="H10" s="8" t="inlineStr">
+        <is>
+          <t>#3423 row 3; #3252 (duplicate-suppression pattern)</t>
+        </is>
+      </c>
+      <c r="I10" s="8" t="inlineStr">
+        <is>
+          <t>reports/cron/changed</t>
+        </is>
+      </c>
+      <c r="J10" s="8" t="inlineStr">
+        <is>
+          <t>Design-issue probe — if two consecutive triggers send two emails, flag as bug and link to #3252.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="15" t="inlineStr">
+        <is>
+          <t>TC-RPT-109</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>Reject notification — rejected period produces APPROVE_REJECT email and flips reject.executor_notified=true</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>Env: ttt-qa-1.
+Manager with a direct report who has approvable hours in an open confirmation period. Reject must have been created at least 5 min ago (DEBOUNCE_INTERVAL_MINUTES=5).
+Query (same manager+employee as TC-RPT-106).</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>SETUP: Via API (as manager) — POST approvable task_reports for the employee in the current confirmation period, then POST a reject for those hours via `POST /api/ttt/v1/rejects` with `cause = 'Session 136 test-reject'`.
+SETUP: Wait ≥ 5 min (or advance clock 5 min on timemachine) so the reject is past DEBOUNCE_INTERVAL_MINUTES.
+SETUP: Clear historical APPROVE_REJECT emails for this employee.
+TRIGGER: `POST /api/ttt/v1/test/reports/notify-rejected`.
+WAIT: 60 s.
+VERIFY LOG: Graylog — **no markers expected from the reject service** (delta #2). Absence of error markers (`"notification FAILED"`) is the success indicator.
+DB-CHECK: `SELECT executor_notified FROM ttt_backend.reject WHERE id = &lt;reject_id&gt;` returns `true`.
+EMAIL-CHECK: Roundcube — employee mailbox receives email with subject `[QA1][TTT] Ваши часы за период &lt;start&gt;-&lt;end&gt; были отклонены менеджером &lt;Manager Russian Name&gt;`.
+CLEANUP: Via API — DELETE the seeded reject and the task_reports.</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>APPROVE_REJECT email dispatched; DB flag `reject.executor_notified` transitions false → true in the same run. No service-level log marker — assertion relies on DB state + email arrival only.</t>
+        </is>
+      </c>
+      <c r="F11" s="15" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="G11" s="15" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>#3423 row 4; delta #2 (no markers)</t>
+        </is>
+      </c>
+      <c r="I11" s="6" t="inlineStr">
+        <is>
+          <t>reports/cron/reject</t>
+        </is>
+      </c>
+      <c r="J11" s="6" t="inlineStr">
+        <is>
+          <t>Delta #2 folded — zero log markers across the reject flow; DB flag + Roundcube subject are the only verification vectors. Subject per patterns/email-notification-triggers §Row 4.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="16" t="inlineStr">
+        <is>
+          <t>TC-RPT-110</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>Reject notification — debounce: reject created &lt;5 min ago is skipped by next run</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>Env: ttt-qa-1 or timemachine.
+Manager+employee pair (same as TC-RPT-109).</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>SETUP: Via API — POST approvable task_reports + a reject (cause='debounce test') **immediately before trigger** (i.e., 0 min ago).
+SETUP: Capture `reject.executor_notified = false`.
+TRIGGER: `POST /api/ttt/v1/test/reports/notify-rejected` within 60 s of reject creation.
+WAIT: 60 s.
+DB-CHECK: `SELECT executor_notified FROM ttt_backend.reject WHERE id = &lt;reject_id&gt;` returns `false` (still, skipped due to debounce).
+EMAIL-CHECK: No APPROVE_REJECT email for this employee yet.
+WAIT: 5–6 min (or advance clock 5 min).
+TRIGGER 2: `POST /api/ttt/v1/test/reports/notify-rejected`.
+WAIT: 60 s.
+DB-CHECK: `executor_notified = true`.
+EMAIL-CHECK: Email now delivered.
+CLEANUP: Via API — DELETE reject + task_reports.</t>
+        </is>
+      </c>
+      <c r="E12" s="8" t="inlineStr">
+        <is>
+          <t>First trigger: debounce skips reject (age &lt; DEBOUNCE_INTERVAL_MINUTES). Second trigger (after 5 min): reject now past debounce → email + flag flip.</t>
+        </is>
+      </c>
+      <c r="F12" s="16" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G12" s="16" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="H12" s="8" t="inlineStr">
+        <is>
+          <t>#3423 row 4; DEBOUNCE_INTERVAL_MINUTES=5</t>
+        </is>
+      </c>
+      <c r="I12" s="8" t="inlineStr">
+        <is>
+          <t>reports/cron/reject</t>
+        </is>
+      </c>
+      <c r="J12" s="8" t="inlineStr">
+        <is>
+          <t>Timing-sensitive. On non-timemachine envs, use real 5-min wait.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="15" t="inlineStr">
+        <is>
+          <t>TC-RPT-111</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>Reject notification — regression #3321: report month closed + confirmation period open still dispatches email</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>Env: ttt-qa-1 or timemachine (requires accountant-level setup).
+Report month = closed (via Accounting → Reporting periods). Confirmation period = OPEN for the same interval.
+Manager+employee pair (same as TC-RPT-109).</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>SETUP: Via API (as accountant) — close the report month covering yesterday but keep the confirmation period open.
+SETUP: Via API (as manager) — POST approvable task_reports for the employee on yesterday, then POST a reject with `cause = 'regression #3321'`. Wait ≥ 5 min.
+SETUP: Clear historical APPROVE_REJECT emails.
+TRIGGER: `POST /api/ttt/v1/test/reports/notify-rejected`.
+WAIT: 60 s.
+DB-CHECK: `reject.executor_notified = true`.
+EMAIL-CHECK: Employee mailbox receives the APPROVE_REJECT email.
+CLEANUP: Via API — DELETE reject; reopen report month if this test polluted the env's period state.</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>Regression #3321 — even with the report month closed, the reject notification still dispatches when the confirmation period is open. Pre-fix, executor_notified stayed false and no email arrived.</t>
+        </is>
+      </c>
+      <c r="F13" s="15" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G13" s="15" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>#3423 row 4; #3321 regression</t>
+        </is>
+      </c>
+      <c r="I13" s="6" t="inlineStr">
+        <is>
+          <t>reports/cron/reject</t>
+        </is>
+      </c>
+      <c r="J13" s="6" t="inlineStr">
+        <is>
+          <t>#3321 Frontend+backend interplay — verify both DB flag AND email arrival.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="16" t="inlineStr">
+        <is>
+          <t>TC-RPT-112</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>Reject notification — idempotency: already-notified reject not re-sent on subsequent runs</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>Env: ttt-qa-1.
+Pre-state: TC-RPT-109 or TC-RPT-111 ran and set `reject.executor_notified = true`.</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>SETUP: Confirm pre-state — `SELECT executor_notified FROM ttt_backend.reject WHERE id = &lt;reject_id&gt;` returns `true`; baseline email count for the employee.
+TRIGGER: `POST /api/ttt/v1/test/reports/notify-rejected`.
+WAIT: 60 s.
+DB-CHECK: `executor_notified` stays `true` (unchanged).
+EMAIL-CHECK: Roundcube — email count unchanged (no new APPROVE_REJECT for this reject_id).
+CLEANUP: None.</t>
+        </is>
+      </c>
+      <c r="E14" s="8" t="inlineStr">
+        <is>
+          <t>Rejects filtered by `executor_notified = false` — once true, the query excludes them on every subsequent run.</t>
+        </is>
+      </c>
+      <c r="F14" s="16" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G14" s="16" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="H14" s="8" t="inlineStr">
+        <is>
+          <t>#3423 row 4</t>
+        </is>
+      </c>
+      <c r="I14" s="8" t="inlineStr">
+        <is>
+          <t>reports/cron/reject</t>
+        </is>
+      </c>
+      <c r="J14" s="8" t="inlineStr">
+        <is>
+          <t>Idempotency via DB-flag predicate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="15" t="inlineStr">
+        <is>
+          <t>TC-RPT-113</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>Extended-period cleanup — expired extended report period transitions to closed</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>Env: ttt-qa-1 or timemachine.
+An `extended_report_period` row exists with `end_date &lt; now()` and `closed = false`.
+Query: SELECT id, employee_id, start_date, end_date FROM ttt_backend.extended_report_period WHERE closed = false AND end_date &lt; NOW() - INTERVAL '1 minute' LIMIT 1;
+If none exists, SETUP must create one.</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>SETUP: If no expired extended period exists, create one via accountant UI/API — `POST /api/ttt/v1/extended-report-periods` with `end_date = NOW() - INTERVAL '1 min'` (or set end_date in the past via DB for timemachine envs).
+SETUP: Capture `closed` value before trigger.
+TRIGGER: `POST /api/ttt/v1/test/reports/cleanup-extended`.
+WAIT: 60 s.
+VERIFY LOG: Graylog — `message:"Extended period clean up started"` → `message:"Extended period clean up finished"` pair within 3 min (both debug level).
+DB-CHECK: `SELECT closed FROM ttt_backend.extended_report_period WHERE id = &lt;row_id&gt;` returns `true`.
+DB-CHECK: No error markers — query `message:"Unable to clean up timed out report extended periods"` is empty in the same window.
+CLEANUP: Delete the seeded extended_report_period row if it was created for this test.</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>Scheduler marks expired extended periods as closed; log markers show start/finish pair; no error marker.</t>
+        </is>
+      </c>
+      <c r="F15" s="15" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="G15" s="15" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>#3423 row 7; #603</t>
+        </is>
+      </c>
+      <c r="I15" s="6" t="inlineStr">
+        <is>
+          <t>reports/cron/extended-cleanup</t>
+        </is>
+      </c>
+      <c r="J15" s="6" t="inlineStr">
+        <is>
+          <t>Happy-path for extended-period scheduler.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="16" t="inlineStr">
+        <is>
+          <t>TC-RPT-114</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>Extended-period — regression #2289: EXTENDED_PERIOD_REPORT email not sent to office accountants</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>Env: ttt-qa-1 or timemachine.
+Env has at least one office accountant and at least one main accountant (role distinction is critical).
+Query: SELECT e.login, r.name FROM ttt_backend.employee e JOIN ttt_backend.employee_role er ON er.employee_id = e.id JOIN ttt_backend.role r ON r.id = er.role_id WHERE e.enabled = true AND r.name IN ('ROLE_OFFICE_ACCOUNTANT', 'ROLE_HEAD_ACCOUNTANT', 'ROLE_DEPARTMENT_MANAGER');</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>SETUP: Reproduce the full EXTENDED_PERIOD_REPORT trigger flow (per #2289 comment by @mpotter):
+  a. Close the report period (distinct from approve period).
+  b. As accountant — reopen the individual report period for a target employee.
+  c. As that employee — report hours on a project.
+  d. As accountant — close the individual report period (or wait 1 hour for auto-close).
+SETUP: Identify office accountant, main accountant, and project manager of the project above.
+SETUP: Clear historical EXTENDED_PERIOD_REPORT emails from ALL three mailboxes (office accountant, main accountant, PM).
+TRIGGER: `POST /api/ttt/v1/test/reports/cleanup-extended` (or wait for scheduler).
+WAIT: 60 s.
+EMAIL-CHECK: Roundcube — MAIN accountant receives EXTENDED_PERIOD_REPORT; PM receives EXTENDED_PERIOD_REPORT; OFFICE accountant does NOT receive it.
+VERIFY LOG: Graylog — extended-cleanup markers fire; `"Sending notification to = "` mentions only main accountant + PM logins, NOT the office accountant login.
+CLEANUP: Revert period state; DELETE seeded task_reports.</t>
+        </is>
+      </c>
+      <c r="E16" s="8" t="inlineStr">
+        <is>
+          <t>Regression #2289 — office accountants must NOT receive EXTENDED_PERIOD_REPORT; only project managers + main accountants do.</t>
+        </is>
+      </c>
+      <c r="F16" s="16" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G16" s="16" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="H16" s="8" t="inlineStr">
+        <is>
+          <t>#3423 row 7; #2289 regression</t>
+        </is>
+      </c>
+      <c r="I16" s="8" t="inlineStr">
+        <is>
+          <t>reports/cron/extended-cleanup</t>
+        </is>
+      </c>
+      <c r="J16" s="8" t="inlineStr">
+        <is>
+          <t>#2289 fix — tighten recipient audience. Setup flow is complex — reference comment thread on ticket.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="15" t="inlineStr">
+        <is>
+          <t>TC-RPT-115</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>Extended-period cleanup — idempotency: already-closed periods remain untouched</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>Env: ttt-qa-1.
+Pre-state: TC-RPT-113 already closed the target extended-period row.</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>SETUP: Confirm `closed = true` in `ttt_backend.extended_report_period WHERE id = &lt;row_id&gt;`; snapshot `updated_at`.
+TRIGGER: `POST /api/ttt/v1/test/reports/cleanup-extended`.
+WAIT: 60 s.
+VERIFY LOG: Graylog — start/finish pair fires, but service should touch 0 rows.
+DB-CHECK: `SELECT updated_at FROM ttt_backend.extended_report_period WHERE id = &lt;row_id&gt;` unchanged from snapshot.
+CLEANUP: None.</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>Query filter `closed = false` excludes this row; cleanup is a no-op.</t>
+        </is>
+      </c>
+      <c r="F17" s="15" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G17" s="15" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>#3423 row 7</t>
+        </is>
+      </c>
+      <c r="I17" s="6" t="inlineStr">
+        <is>
+          <t>reports/cron/extended-cleanup</t>
+        </is>
+      </c>
+      <c r="J17" s="6" t="inlineStr">
+        <is>
+          <t>Idempotency via closed-flag predicate.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00F4B084"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="45" customWidth="1" min="3" max="3"/>
+    <col width="72" customWidth="1" min="4" max="4"/>
+    <col width="45" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="8" max="8"/>
+    <col width="26" customWidth="1" min="9" max="9"/>
+    <col width="35" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4">
+        <f>HYPERLINK("#'Plan Overview'!A1", "← Back to Plan Overview")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="14" t="inlineStr">
+        <is>
+          <t>Test ID</t>
+        </is>
+      </c>
+      <c r="B2" s="14" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="C2" s="14" t="inlineStr">
+        <is>
+          <t>Preconditions</t>
+        </is>
+      </c>
+      <c r="D2" s="14" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="E2" s="14" t="inlineStr">
+        <is>
+          <t>Expected Result</t>
+        </is>
+      </c>
+      <c r="F2" s="14" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="G2" s="14" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="H2" s="14" t="inlineStr">
+        <is>
+          <t>Requirement Ref</t>
+        </is>
+      </c>
+      <c r="I2" s="14" t="inlineStr">
+        <is>
+          <t>Module/Component</t>
+        </is>
+      </c>
+      <c r="J2" s="14" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="15" t="inlineStr">
+        <is>
+          <t>TC-RPT-116</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>Budget notification — EXCEEDED: first crossing of budget_limit dispatches BUDGET_NOTIFICATION_EXCEEDED</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>Env: ttt-qa-1.
+A `BudgetNotification` entity seeded for a (project, employee, date range) with budget_limit = 4 hours. Target employee has NOT yet reported hours in the window.
+Query to pick a project+employee: SELECT p.id, p.name, e.login FROM ttt_backend.project p JOIN ttt_backend.employee_project ep ON ep.project_id = p.id JOIN ttt_backend.employee e ON e.id = ep.employee_id WHERE p.status = 'ACTIVE' AND e.enabled = true AND e.login &lt;&gt; 'pvaynmaster' ORDER BY random() LIMIT 1;</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>SETUP: Pick an active (project, employee, manager-watcher) triple.
+SETUP: Via API — `POST /api/ttt/v1/budget-notifications` with watcher_id = &lt;mgr_id&gt;, project_id = &lt;project_id&gt;, employee_id = &lt;emp_id&gt;, budget_limit = 240 (4 hours in minutes), start_date = today, end_date = today.
+SETUP: Clear historical BUDGET_NOTIFICATION_EXCEEDED emails from watcher's mailbox.
+STEP (UI): Login as the employee; navigate to My Tasks; report 5 hours on a task of &lt;project_id&gt; for today.
+STEP: Wait ≥ 10 s (SAFETY_INTERVAL_SECONDS) so the task_report is considered stable.
+TRIGGER: `POST /api/ttt/v1/test/budgets/notify`.
+WAIT: 30 s (scheduler cadence + email-send cadence).
+VERIFY LOG: Graylog — `message:"Budget notification job is done"` fires (info).
+DB-CHECK: `SELECT limit_reached_date FROM ttt_backend.budget_notification WHERE id = &lt;notif_id&gt;` is non-null and equals today.
+EMAIL-CHECK: Roundcube — watcher mailbox receives email whose template key maps to `BUDGET_NOTIFICATION_EXCEEDED`.
+CLEANUP: Via API — DELETE the seeded BudgetNotification and the task_report.</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>First budget crossing — BudgetServiceImpl detects prev=null → current=today transition; dispatches EXCEEDED template to watcher.</t>
+        </is>
+      </c>
+      <c r="F3" s="15" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="G3" s="15" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="H3" s="6" t="inlineStr">
+        <is>
+          <t>#3423 row 5; delta #3 (three templates); #892 regression</t>
+        </is>
+      </c>
+      <c r="I3" s="6" t="inlineStr">
+        <is>
+          <t>reports/cron/budget</t>
+        </is>
+      </c>
+      <c r="J3" s="6" t="inlineStr">
+        <is>
+          <t>Delta #3 folded — template is BUDGET_NOTIFICATION_EXCEEDED. SAFETY_INTERVAL_SECONDS=10 means recent task_reports are skipped.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="16" t="inlineStr">
+        <is>
+          <t>TC-RPT-117</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>Budget notification — NOT_REACHED: exceeded budget then reduced dispatches BUDGET_NOTIFICATION_NOT_REACHED</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>Env: ttt-qa-1.
+Pre-state: TC-RPT-116 dispatched EXCEEDED; `limit_reached_date = today`.</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>SETUP: Confirm pre-state — `limit_reached_date` non-null for &lt;notif_id&gt;.
+STEP (UI): Login as the employee; navigate to My Tasks; edit the 5h entry down to 2h for today.
+STEP: Wait ≥ 10 s.
+TRIGGER: `POST /api/ttt/v1/test/budgets/notify`.
+WAIT: 30 s.
+DB-CHECK: `limit_reached_date` now `null` (prev=today → current=null transition).
+EMAIL-CHECK: Watcher mailbox receives email matching BUDGET_NOTIFICATION_NOT_REACHED.
+VERIFY LOG: `"Budget notification job is done"` fires.
+CLEANUP: Delete seeded entities.</t>
+        </is>
+      </c>
+      <c r="E4" s="8" t="inlineStr">
+        <is>
+          <t>Budget fell below limit — NOT_REACHED template dispatched. limit_reached_date cleared back to null.</t>
+        </is>
+      </c>
+      <c r="F4" s="16" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G4" s="16" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="H4" s="8" t="inlineStr">
+        <is>
+          <t>#3423 row 5; delta #3; #892 regression</t>
+        </is>
+      </c>
+      <c r="I4" s="8" t="inlineStr">
+        <is>
+          <t>reports/cron/budget</t>
+        </is>
+      </c>
+      <c r="J4" s="8" t="inlineStr">
+        <is>
+          <t>Template key BUDGET_NOTIFICATION_NOT_REACHED.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="15" t="inlineStr">
+        <is>
+          <t>TC-RPT-118</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>Budget notification — DATE_UPDATED: hours moved to a different day keeping budget exceeded</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>Env: ttt-qa-1.
+Pre-state: TC-RPT-116 dispatched EXCEEDED for today's report.</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>SETUP: Confirm `limit_reached_date = today` in DB.
+STEP (UI): Login as employee; move today's 5h entry to yesterday (delete today's report, create an identical one for yesterday with 5h).
+SETUP: Via API (if UI does not allow yesterday edit) — DELETE today's task_report; POST the same hours on yesterday.
+STEP: Wait ≥ 10 s.
+TRIGGER: `POST /api/ttt/v1/test/budgets/notify`.
+WAIT: 30 s.
+DB-CHECK: `limit_reached_date` changed from today → yesterday.
+EMAIL-CHECK: Watcher receives email matching BUDGET_NOTIFICATION_DATE_UPDATED.
+CLEANUP: Delete seeded entities.</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>Budget still exceeded but on a different date — DATE_UPDATED template dispatched.</t>
+        </is>
+      </c>
+      <c r="F5" s="15" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G5" s="15" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="H5" s="6" t="inlineStr">
+        <is>
+          <t>#3423 row 5; delta #3; #892 regression</t>
+        </is>
+      </c>
+      <c r="I5" s="6" t="inlineStr">
+        <is>
+          <t>reports/cron/budget</t>
+        </is>
+      </c>
+      <c r="J5" s="6" t="inlineStr">
+        <is>
+          <t>Template key BUDGET_NOTIFICATION_DATE_UPDATED.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="16" t="inlineStr">
+        <is>
+          <t>TC-RPT-119</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>Budget notification — safety window: task_report younger than 10 s is skipped by next run</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>Env: ttt-qa-1.
+Seeded BudgetNotification (same shape as TC-RPT-116).</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>SETUP: Seed BudgetNotification as in TC-RPT-116; confirm `limit_reached_date = null`.
+STEP (UI): Report 5h on the project for today.
+TRIGGER: `POST /api/ttt/v1/test/budgets/notify` within 5 s of the report (definitely &lt; SAFETY_INTERVAL_SECONDS=10).
+WAIT: 30 s.
+DB-CHECK: `limit_reached_date` still `null` (skipped — too recent).
+EMAIL-CHECK: No BUDGET_NOTIFICATION_EXCEEDED email yet.
+WAIT: additional 15 s (total ~20 s past the report).
+TRIGGER 2: `POST /api/ttt/v1/test/budgets/notify`.
+WAIT: 30 s.
+DB-CHECK: `limit_reached_date = today` now.
+EMAIL-CHECK: Email arrives.
+CLEANUP: Delete seeded entities.</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>SAFETY_INTERVAL_SECONDS=10 guards against flapping; first trigger skips, second trigger (after safety window) dispatches.</t>
+        </is>
+      </c>
+      <c r="F6" s="16" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G6" s="16" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="H6" s="8" t="inlineStr">
+        <is>
+          <t>#3423 row 5; delta #3 (SAFETY_INTERVAL_SECONDS=10)</t>
+        </is>
+      </c>
+      <c r="I6" s="8" t="inlineStr">
+        <is>
+          <t>reports/cron/budget</t>
+        </is>
+      </c>
+      <c r="J6" s="8" t="inlineStr">
+        <is>
+          <t>Timing-sensitive. Real-time env; cannot advance clock easily here.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="15" t="inlineStr">
+        <is>
+          <t>TC-RPT-120</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>Budget notification — recipient: email goes to watcher_id, not employee</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>Env: ttt-qa-1.
+Seeded BudgetNotification with watcher_id = &lt;mgr_id&gt;, employee_id = &lt;emp_id&gt;, and mgr_id ≠ emp_id.</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>SETUP: Seed as in TC-RPT-116 with distinct watcher and employee.
+SETUP: Clear BUDGET_NOTIFICATION_EXCEEDED emails from BOTH mailboxes.
+STEP (UI): Employee reports 5h for today on the project.
+STEP: Wait 15 s (past SAFETY_INTERVAL).
+TRIGGER: `POST /api/ttt/v1/test/budgets/notify`.
+WAIT: 30 s.
+EMAIL-CHECK: Watcher's mailbox has ONE new EXCEEDED email; employee's mailbox has ZERO new BUDGET_* emails.
+VERIFY LOG: `"Budget notification job is done"` fires.
+CLEANUP: Delete seeded entities.</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>Email sent only to `notification.watcherId` resolved via employeeService.find(watcherId); employee never receives a copy.</t>
+        </is>
+      </c>
+      <c r="F7" s="15" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G7" s="15" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>#3423 row 5</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>reports/cron/budget</t>
+        </is>
+      </c>
+      <c r="J7" s="6" t="inlineStr">
+        <is>
+          <t>Recipient-correctness guard.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/test-docs/reports/reports.xlsx
+++ b/test-docs/reports/reports.xlsx
@@ -17,8 +17,6 @@
     <sheet name="TS-Reports-Statistics" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="TS-Reports-Notifications" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="TS-Reports-Permissions" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="TS-Reports-CronNotifications" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="TS-Reports-BudgetNotifications" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'TS-Reports-CRUD'!$A$2:$J$17</definedName>
@@ -1362,1413 +1360,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="00F4B084"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:J17"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="45" customWidth="1" min="3" max="3"/>
-    <col width="72" customWidth="1" min="4" max="4"/>
-    <col width="45" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="35" customWidth="1" min="8" max="8"/>
-    <col width="26" customWidth="1" min="9" max="9"/>
-    <col width="35" customWidth="1" min="10" max="10"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="4">
-        <f>HYPERLINK("#'Plan Overview'!A1", "← Back to Plan Overview")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="14" t="inlineStr">
-        <is>
-          <t>Test ID</t>
-        </is>
-      </c>
-      <c r="B2" s="14" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
-      <c r="C2" s="14" t="inlineStr">
-        <is>
-          <t>Preconditions</t>
-        </is>
-      </c>
-      <c r="D2" s="14" t="inlineStr">
-        <is>
-          <t>Steps</t>
-        </is>
-      </c>
-      <c r="E2" s="14" t="inlineStr">
-        <is>
-          <t>Expected Result</t>
-        </is>
-      </c>
-      <c r="F2" s="14" t="inlineStr">
-        <is>
-          <t>Priority</t>
-        </is>
-      </c>
-      <c r="G2" s="14" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="H2" s="14" t="inlineStr">
-        <is>
-          <t>Requirement Ref</t>
-        </is>
-      </c>
-      <c r="I2" s="14" t="inlineStr">
-        <is>
-          <t>Module/Component</t>
-        </is>
-      </c>
-      <c r="J2" s="14" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="15" t="inlineStr">
-        <is>
-          <t>TC-RPT-101</t>
-        </is>
-      </c>
-      <c r="B3" s="6" t="inlineStr">
-        <is>
-          <t>Forgotten-report notification — underreported employee receives weekly email</t>
-        </is>
-      </c>
-      <c r="C3" s="6" t="inlineStr">
-        <is>
-          <t>Env: ttt-timemachine (clock controllable) or ttt-qa-1.
-Employee must be enabled, NOT in officeId=9 (per regression #685), and must have reported less than the weekly norm for the previous report period (taking vacations/absences into account).
-Query: SELECT e.login FROM ttt_backend.employee e JOIN ttt_backend.office o ON e.salary_office_id = o.id WHERE e.enabled = true AND o.id &lt;&gt; 9 AND NOT EXISTS (  SELECT 1 FROM ttt_backend.task_report tr   WHERE tr.executor_id = e.id   AND tr.report_date BETWEEN (current_date - INTERVAL '7 days') AND (current_date - INTERVAL '1 day')) ORDER BY random() LIMIT 1;</t>
-        </is>
-      </c>
-      <c r="D3" s="6" t="inlineStr">
-        <is>
-          <t>SETUP: Pick an underreported employee from the query above.
-SETUP: Clear any historical FORGOTTEN_REPORT emails via `roundcube-access --delete --subject '[QA1][TTT] Скорее всего вы забыли'` for that mailbox (or note baseline UID).
-TRIGGER: `POST /api/ttt/v1/test/reports/notify-forgotten` (empty body, requires API_SECRET_TOKEN).
-WAIT: ~60 s for EmailSendScheduler (every 20 s) to dispatch.
-VERIFY LOG: Graylog TTT-QA-1 — `message:"Report forgotten notification started"` within last 3 min (debug level).
-VERIFY LOG: Graylog TTT-QA-1 — `message:"Employees not reached reporting norm count = "` with count ≥ 1.
-EMAIL-CHECK: `roundcube-access search --since today --subject '[QA1][TTT]' --subject 'Скорее всего вы забыли зарепортиться за прошлую неделю' --to &lt;employee-email&gt;` returns ≥ 1 message.
-CLEANUP: None (idempotent email noise; next run will re-evaluate).</t>
-        </is>
-      </c>
-      <c r="E3" s="6" t="inlineStr">
-        <is>
-          <t>Employee's mailbox receives FORGOTTEN_REPORT email (template key `FORGOTTEN_REPORT`). Graylog shows the scheduler marker and the "Employees not reached reporting norm" count reflects the test subject employee.</t>
-        </is>
-      </c>
-      <c r="F3" s="15" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="G3" s="15" t="inlineStr">
-        <is>
-          <t>Hybrid</t>
-        </is>
-      </c>
-      <c r="H3" s="6" t="inlineStr">
-        <is>
-          <t>#3423 row 1; #559</t>
-        </is>
-      </c>
-      <c r="I3" s="6" t="inlineStr">
-        <is>
-          <t>reports/cron/forgotten</t>
-        </is>
-      </c>
-      <c r="J3" s="6" t="inlineStr">
-        <is>
-          <t>Subject per email-notification-triggers §Row 1.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="16" t="inlineStr">
-        <is>
-          <t>TC-RPT-102</t>
-        </is>
-      </c>
-      <c r="B4" s="8" t="inlineStr">
-        <is>
-          <t>Forgotten-report — employees with salary_office_id=9 (Office not assigned) excluded</t>
-        </is>
-      </c>
-      <c r="C4" s="8" t="inlineStr">
-        <is>
-          <t>Env: ttt-qa-1.
-At least one enabled employee with `salary_office_id = 9` who is underreported for the previous report period.
-Query: SELECT e.login FROM ttt_backend.employee e WHERE e.enabled = true AND e.salary_office_id = 9 LIMIT 1;</t>
-        </is>
-      </c>
-      <c r="D4" s="8" t="inlineStr">
-        <is>
-          <t>SETUP: Identify target employee with officeId=9.
-SETUP: Clear historical FORGOTTEN_REPORT emails for this mailbox.
-TRIGGER: `POST /api/ttt/v1/test/reports/notify-forgotten`.
-WAIT: 60 s.
-VERIFY LOG: Graylog shows scheduler marker fired (global — `message:"Report forgotten notification started"`).
-VERIFY LOG: Verify `"Sending notification to = "` does NOT mention this employee's login in last 5 min.
-EMAIL-CHECK: `roundcube-access search --since today --to &lt;employee-email&gt; --subject 'Скорее всего'` returns 0 messages.
-DB-CHECK: No `notification_log` insert (if applicable) for this employee in last 5 min.
-CLEANUP: None.</t>
-        </is>
-      </c>
-      <c r="E4" s="8" t="inlineStr">
-        <is>
-          <t>Even when the employee meets the underreport predicate, the office filter (officeId != 9) excludes them. Other employees may still be notified — verify the scope table via the service-level count marker.</t>
-        </is>
-      </c>
-      <c r="F4" s="16" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G4" s="16" t="inlineStr">
-        <is>
-          <t>Hybrid</t>
-        </is>
-      </c>
-      <c r="H4" s="8" t="inlineStr">
-        <is>
-          <t>#3423 row 1; #685 regression</t>
-        </is>
-      </c>
-      <c r="I4" s="8" t="inlineStr">
-        <is>
-          <t>reports/cron/forgotten</t>
-        </is>
-      </c>
-      <c r="J4" s="8" t="inlineStr">
-        <is>
-          <t>#685 fix guard — 'Office not assigned' employees never get weekly reminder.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="15" t="inlineStr">
-        <is>
-          <t>TC-RPT-103</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>Forgotten-report — fully-reported employee excluded</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="inlineStr">
-        <is>
-          <t>Env: ttt-qa-1.
-Enabled employee with all workdays of the previous report period fully reported (effort_sum ≥ norm, ignoring vacations/sick leave).
-Query: SELECT e.login FROM ttt_backend.employee e JOIN (SELECT executor_id, SUM(effort) AS total_min   FROM ttt_backend.task_report   WHERE report_date BETWEEN (current_date - INTERVAL '7 days')   AND (current_date - INTERVAL '1 day')   GROUP BY executor_id) tr ON tr.executor_id = e.id WHERE e.enabled = true AND tr.total_min &gt;= 40 * 60 ORDER BY random() LIMIT 1;</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>SETUP: Pick a fully-reported employee.
-SETUP: Clear historical FORGOTTEN_REPORT emails for this mailbox.
-TRIGGER: `POST /api/ttt/v1/test/reports/notify-forgotten`.
-WAIT: 60 s.
-EMAIL-CHECK: `roundcube-access search --since today --to &lt;employee-email&gt; --subject 'Скорее всего'` returns 0 messages.
-VERIFY LOG: `"Sending notification to = "` does NOT mention this employee.
-CLEANUP: None.</t>
-        </is>
-      </c>
-      <c r="E5" s="6" t="inlineStr">
-        <is>
-          <t>Query predicate `not_reached_norm = true` filters out this employee; no email dispatched despite scheduler firing.</t>
-        </is>
-      </c>
-      <c r="F5" s="15" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G5" s="15" t="inlineStr">
-        <is>
-          <t>Hybrid</t>
-        </is>
-      </c>
-      <c r="H5" s="6" t="inlineStr">
-        <is>
-          <t>#3423 row 1; #559</t>
-        </is>
-      </c>
-      <c r="I5" s="6" t="inlineStr">
-        <is>
-          <t>reports/cron/forgotten</t>
-        </is>
-      </c>
-      <c r="J5" s="6" t="inlineStr">
-        <is>
-          <t>Norm-reached negative path.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="16" t="inlineStr">
-        <is>
-          <t>TC-RPT-104</t>
-        </is>
-      </c>
-      <c r="B6" s="8" t="inlineStr">
-        <is>
-          <t>Forgotten-delayed notification — employee who remained underreported receives catch-up email</t>
-        </is>
-      </c>
-      <c r="C6" s="8" t="inlineStr">
-        <is>
-          <t>Env: ttt-timemachine (clock control recommended).
-Enabled employee who received the first FORGOTTEN_REPORT on Mon/Fri 16:00 NSK and has STILL not reported by 16:30 NSK the same day.
-Query: same base as TC-RPT-101.</t>
-        </is>
-      </c>
-      <c r="D6" s="8" t="inlineStr">
-        <is>
-          <t>SETUP: Pick underreported employee (query from TC-RPT-101).
-SETUP: Clear historical FORGOTTEN_REPORT emails.
-TRIGGER 1: `POST /api/ttt/v1/test/reports/notify-forgotten` (simulate the 16:00 first pass).
-WAIT: 60 s; verify one FORGOTTEN_REPORT email dispatched.
-TRIGGER 2: `POST /api/ttt/v1/test/reports/notify-forgotten-delayed` (simulate the 16:30 delayed pass).
-WAIT: 60 s.
-VERIFY LOG: Graylog — `message:"Report forgotten delayed notification started"` (debug).
-VERIFY LOG: `message:"Sending delayed notification to = "` mentions the employee.
-EMAIL-CHECK: Roundcube — employee's mailbox now shows TWO messages matching the FORGOTTEN_REPORT subject, sent ~30 min apart.
-CLEANUP: None.</t>
-        </is>
-      </c>
-      <c r="E6" s="8" t="inlineStr">
-        <is>
-          <t>Delayed path sends a second FORGOTTEN_REPORT email (same template, different invocation) for employees who remain underreported after the first pass.</t>
-        </is>
-      </c>
-      <c r="F6" s="16" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G6" s="16" t="inlineStr">
-        <is>
-          <t>Hybrid</t>
-        </is>
-      </c>
-      <c r="H6" s="8" t="inlineStr">
-        <is>
-          <t>#3423 row 2; #559</t>
-        </is>
-      </c>
-      <c r="I6" s="8" t="inlineStr">
-        <is>
-          <t>reports/cron/forgotten-delayed</t>
-        </is>
-      </c>
-      <c r="J6" s="8" t="inlineStr">
-        <is>
-          <t>Subject predicate identical to row 1 — disambiguate via send-time (~16:30) or via log marker ‘delayed notification to ='.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="15" t="inlineStr">
-        <is>
-          <t>TC-RPT-105</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>Forgotten-delayed — employee who reported after the 16:00 pass is excluded</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>Env: ttt-timemachine.
-Employee received FORGOTTEN_REPORT at 16:00 NSK pass, then submitted reports to close the deficit before 16:30 NSK.</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>SETUP: Pick underreported employee; dispatch first FORGOTTEN_REPORT via `/notify-forgotten`.
-SETUP: Via API (as that employee) — POST missing task_reports to reach weekly norm.
-TRIGGER: `POST /api/ttt/v1/test/reports/notify-forgotten-delayed`.
-WAIT: 60 s.
-VERIFY LOG: `message:"Employee {} already reported hours for period from {} to {}"` mentions this employee.
-EMAIL-CHECK: Roundcube — only ONE FORGOTTEN_REPORT email for this employee (from the first pass), not two.
-CLEANUP: Delete the seeded task_reports if test data hygiene requires.</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>Delayed-pass skips employees whose norm gap was closed between 16:00 and 16:30 (service-level log marker `already reported` confirms the skip).</t>
-        </is>
-      </c>
-      <c r="F7" s="15" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G7" s="15" t="inlineStr">
-        <is>
-          <t>Hybrid</t>
-        </is>
-      </c>
-      <c r="H7" s="6" t="inlineStr">
-        <is>
-          <t>#3423 row 2; #559</t>
-        </is>
-      </c>
-      <c r="I7" s="6" t="inlineStr">
-        <is>
-          <t>reports/cron/forgotten-delayed</t>
-        </is>
-      </c>
-      <c r="J7" s="6" t="inlineStr">
-        <is>
-          <t>Negative path using the `already reported` marker as witness.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="16" t="inlineStr">
-        <is>
-          <t>TC-RPT-106</t>
-        </is>
-      </c>
-      <c r="B8" s="8" t="inlineStr">
-        <is>
-          <t>Reports-changed notification — manager edits employee hours → REPORT_SHEET_CHANGED email</t>
-        </is>
-      </c>
-      <c r="C8" s="8" t="inlineStr">
-        <is>
-          <t>Env: ttt-qa-1.
-Manager with a direct report. Manager and employee must be different users (predicate `reporter_id != executor_id`).
-Query for manager+employee pair: SELECT mgr.login AS mgr_login, emp.login AS emp_login FROM ttt_backend.employee emp JOIN ttt_backend.employee mgr ON emp.manager_id = mgr.id WHERE emp.enabled = true AND mgr.enabled = true AND mgr.login &lt;&gt; 'pvaynmaster' ORDER BY random() LIMIT 1;</t>
-        </is>
-      </c>
-      <c r="D8" s="8" t="inlineStr">
-        <is>
-          <t>SETUP: Resolve the (manager, employee) pair.
-SETUP: Ensure the employee has at least one task on an active project shared with the manager (join via employee_project).
-SETUP: Clear historical REPORT_SHEET_CHANGED emails for the employee.
-STEP 1: Login as MANAGER via browser.
-STEP 2: Navigate to Employees &amp; Contractors → find the subordinate.
-STEP 3: Open the weekly report sheet for YESTERDAY.
-STEP 4: Click an empty cell for an assigned task, enter 2 (hours), press Enter.
-STEP 5: Verify the cell saves with manager as reporter (reporter_id = manager.id, executor_id = employee.id).
-TRIGGER: `POST /api/ttt/v1/test/reports/notify-changed`.
-WAIT: 60 s.
-VERIFY LOG: Graylog — `message:"Start notification process"` AND `message:"Find: "` with count ≥ 1.
-EMAIL-CHECK: Roundcube — employee mailbox receives email with template data referencing the manager's name and the edited date. Subject must match the REPORT_SHEET_CHANGED predicate (captured in session 136 during first real seeding run — record the exact subject as a P2 follow-up for patterns/email-notification-triggers.md row 3).
-DB-CHECK: `SELECT reporter_id, executor_id FROM ttt_backend.task_report WHERE report_date = current_date - 1 AND reporter_id = &lt;mgr_id&gt; AND executor_id = &lt;emp_id&gt;` returns ≥ 1 row.
-CLEANUP: Via API — DELETE the manager-reported task_report rows.</t>
-        </is>
-      </c>
-      <c r="E8" s="8" t="inlineStr">
-        <is>
-          <t>Template `REPORT_SHEET_CHANGED` (NOT TASK_REPORT_CHANGED — per delta #1) fires for yesterday's manager-reported rows. Email arrives grouped by (manager, report_date).</t>
-        </is>
-      </c>
-      <c r="F8" s="16" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="G8" s="16" t="inlineStr">
-        <is>
-          <t>Hybrid</t>
-        </is>
-      </c>
-      <c r="H8" s="8" t="inlineStr">
-        <is>
-          <t>#3423 row 3; delta #1 (template key); #570</t>
-        </is>
-      </c>
-      <c r="I8" s="8" t="inlineStr">
-        <is>
-          <t>reports/cron/changed</t>
-        </is>
-      </c>
-      <c r="J8" s="8" t="inlineStr">
-        <is>
-          <t>Delta #1 folded: template key is REPORT_SHEET_CHANGED — scope table said TASK_REPORT_CHANGED (incorrect). Predicate: reporter_id ≠ executor_id AND report_date = yesterday.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="15" t="inlineStr">
-        <is>
-          <t>TC-RPT-107</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>Reports-changed — manager edits OWN hours does NOT fire REPORT_SHEET_CHANGED</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>Env: ttt-qa-1.
-Any manager with assigned tasks (self-report scenario).
-Query: same as TC-RPT-106 mgr_login.</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>SETUP: Pick a manager.
-SETUP: Clear historical REPORT_SHEET_CHANGED emails.
-STEP 1: Login as MANAGER via browser.
-STEP 2: Navigate to My Tasks → report 2 hours for yesterday on an assigned task.
-STEP 3: Verify `reporter_id = executor_id = manager.id` in DB.
-TRIGGER: `POST /api/ttt/v1/test/reports/notify-changed`.
-WAIT: 60 s.
-VERIFY LOG: `message:"Find: 0 task reported by manager today"` (or count excludes this row).
-EMAIL-CHECK: Roundcube — no REPORT_SHEET_CHANGED email for this manager.
-DB-CHECK: No row matches `reporter_id != executor_id AND report_date = current_date - 1` from this manager's edits.
-CLEANUP: Via API — DELETE the seeded row.</t>
-        </is>
-      </c>
-      <c r="E9" s="6" t="inlineStr">
-        <is>
-          <t>Query predicate `reporter_id != executor_id` excludes self-reports; no email dispatched.</t>
-        </is>
-      </c>
-      <c r="F9" s="15" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G9" s="15" t="inlineStr">
-        <is>
-          <t>Hybrid</t>
-        </is>
-      </c>
-      <c r="H9" s="6" t="inlineStr">
-        <is>
-          <t>#3423 row 3</t>
-        </is>
-      </c>
-      <c r="I9" s="6" t="inlineStr">
-        <is>
-          <t>reports/cron/changed</t>
-        </is>
-      </c>
-      <c r="J9" s="6" t="inlineStr">
-        <is>
-          <t>Negative path — executor-equals-reporter filter.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="16" t="inlineStr">
-        <is>
-          <t>TC-RPT-108</t>
-        </is>
-      </c>
-      <c r="B10" s="8" t="inlineStr">
-        <is>
-          <t>Reports-changed — idempotency on repeated trigger within the same day</t>
-        </is>
-      </c>
-      <c r="C10" s="8" t="inlineStr">
-        <is>
-          <t>Env: ttt-qa-1.
-Pre-state: TC-RPT-106 ran today and dispatched a REPORT_SHEET_CHANGED email.</t>
-        </is>
-      </c>
-      <c r="D10" s="8" t="inlineStr">
-        <is>
-          <t>SETUP: Capture baseline email count for the affected employee (`roundcube-access count --since today --to &lt;emp-email&gt; --subject 'REPORT_SHEET_CHANGED-subject'`).
-TRIGGER 1: `POST /api/ttt/v1/test/reports/notify-changed` (within 5–10 min of the TC-RPT-106 run).
-WAIT: 60 s.
-TRIGGER 2: `POST /api/ttt/v1/test/reports/notify-changed` (second invocation).
-WAIT: 60 s.
-VERIFY LOG: Both invocations log `Start notification process`; `Find: N` count is the SAME on both runs (the service re-selects yesterday's rows every time).
-EMAIL-CHECK: Roundcube — post-trigger email count equals baseline + N (where N = rows found first time). Second trigger does NOT add emails UNLESS new manager-reported rows landed in between.
-CLEANUP: None.</t>
-        </is>
-      </c>
-      <c r="E10" s="8" t="inlineStr">
-        <is>
-          <t>Current code sends on EVERY invocation — idempotency is enforced by an `already_notified` DB flag on task_report (if present) or by the 5-minute scheduler cadence, not by the test endpoint. Document observed behavior; file a design-issue note if duplicates appear.</t>
-        </is>
-      </c>
-      <c r="F10" s="16" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G10" s="16" t="inlineStr">
-        <is>
-          <t>Hybrid</t>
-        </is>
-      </c>
-      <c r="H10" s="8" t="inlineStr">
-        <is>
-          <t>#3423 row 3; #3252 (duplicate-suppression pattern)</t>
-        </is>
-      </c>
-      <c r="I10" s="8" t="inlineStr">
-        <is>
-          <t>reports/cron/changed</t>
-        </is>
-      </c>
-      <c r="J10" s="8" t="inlineStr">
-        <is>
-          <t>Design-issue probe — if two consecutive triggers send two emails, flag as bug and link to #3252.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="15" t="inlineStr">
-        <is>
-          <t>TC-RPT-109</t>
-        </is>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>Reject notification — rejected period produces APPROVE_REJECT email and flips reject.executor_notified=true</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>Env: ttt-qa-1.
-Manager with a direct report who has approvable hours in an open confirmation period. Reject must have been created at least 5 min ago (DEBOUNCE_INTERVAL_MINUTES=5).
-Query (same manager+employee as TC-RPT-106).</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>SETUP: Via API (as manager) — POST approvable task_reports for the employee in the current confirmation period, then POST a reject for those hours via `POST /api/ttt/v1/rejects` with `cause = 'Session 136 test-reject'`.
-SETUP: Wait ≥ 5 min (or advance clock 5 min on timemachine) so the reject is past DEBOUNCE_INTERVAL_MINUTES.
-SETUP: Clear historical APPROVE_REJECT emails for this employee.
-TRIGGER: `POST /api/ttt/v1/test/reports/notify-rejected`.
-WAIT: 60 s.
-VERIFY LOG: Graylog — **no markers expected from the reject service** (delta #2). Absence of error markers (`"notification FAILED"`) is the success indicator.
-DB-CHECK: `SELECT executor_notified FROM ttt_backend.reject WHERE id = &lt;reject_id&gt;` returns `true`.
-EMAIL-CHECK: Roundcube — employee mailbox receives email with subject `[QA1][TTT] Ваши часы за период &lt;start&gt;-&lt;end&gt; были отклонены менеджером &lt;Manager Russian Name&gt;`.
-CLEANUP: Via API — DELETE the seeded reject and the task_reports.</t>
-        </is>
-      </c>
-      <c r="E11" s="6" t="inlineStr">
-        <is>
-          <t>APPROVE_REJECT email dispatched; DB flag `reject.executor_notified` transitions false → true in the same run. No service-level log marker — assertion relies on DB state + email arrival only.</t>
-        </is>
-      </c>
-      <c r="F11" s="15" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="G11" s="15" t="inlineStr">
-        <is>
-          <t>Hybrid</t>
-        </is>
-      </c>
-      <c r="H11" s="6" t="inlineStr">
-        <is>
-          <t>#3423 row 4; delta #2 (no markers)</t>
-        </is>
-      </c>
-      <c r="I11" s="6" t="inlineStr">
-        <is>
-          <t>reports/cron/reject</t>
-        </is>
-      </c>
-      <c r="J11" s="6" t="inlineStr">
-        <is>
-          <t>Delta #2 folded — zero log markers across the reject flow; DB flag + Roundcube subject are the only verification vectors. Subject per patterns/email-notification-triggers §Row 4.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="16" t="inlineStr">
-        <is>
-          <t>TC-RPT-110</t>
-        </is>
-      </c>
-      <c r="B12" s="8" t="inlineStr">
-        <is>
-          <t>Reject notification — debounce: reject created &lt;5 min ago is skipped by next run</t>
-        </is>
-      </c>
-      <c r="C12" s="8" t="inlineStr">
-        <is>
-          <t>Env: ttt-qa-1 or timemachine.
-Manager+employee pair (same as TC-RPT-109).</t>
-        </is>
-      </c>
-      <c r="D12" s="8" t="inlineStr">
-        <is>
-          <t>SETUP: Via API — POST approvable task_reports + a reject (cause='debounce test') **immediately before trigger** (i.e., 0 min ago).
-SETUP: Capture `reject.executor_notified = false`.
-TRIGGER: `POST /api/ttt/v1/test/reports/notify-rejected` within 60 s of reject creation.
-WAIT: 60 s.
-DB-CHECK: `SELECT executor_notified FROM ttt_backend.reject WHERE id = &lt;reject_id&gt;` returns `false` (still, skipped due to debounce).
-EMAIL-CHECK: No APPROVE_REJECT email for this employee yet.
-WAIT: 5–6 min (or advance clock 5 min).
-TRIGGER 2: `POST /api/ttt/v1/test/reports/notify-rejected`.
-WAIT: 60 s.
-DB-CHECK: `executor_notified = true`.
-EMAIL-CHECK: Email now delivered.
-CLEANUP: Via API — DELETE reject + task_reports.</t>
-        </is>
-      </c>
-      <c r="E12" s="8" t="inlineStr">
-        <is>
-          <t>First trigger: debounce skips reject (age &lt; DEBOUNCE_INTERVAL_MINUTES). Second trigger (after 5 min): reject now past debounce → email + flag flip.</t>
-        </is>
-      </c>
-      <c r="F12" s="16" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G12" s="16" t="inlineStr">
-        <is>
-          <t>Hybrid</t>
-        </is>
-      </c>
-      <c r="H12" s="8" t="inlineStr">
-        <is>
-          <t>#3423 row 4; DEBOUNCE_INTERVAL_MINUTES=5</t>
-        </is>
-      </c>
-      <c r="I12" s="8" t="inlineStr">
-        <is>
-          <t>reports/cron/reject</t>
-        </is>
-      </c>
-      <c r="J12" s="8" t="inlineStr">
-        <is>
-          <t>Timing-sensitive. On non-timemachine envs, use real 5-min wait.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="15" t="inlineStr">
-        <is>
-          <t>TC-RPT-111</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>Reject notification — regression #3321: report month closed + confirmation period open still dispatches email</t>
-        </is>
-      </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>Env: ttt-qa-1 or timemachine (requires accountant-level setup).
-Report month = closed (via Accounting → Reporting periods). Confirmation period = OPEN for the same interval.
-Manager+employee pair (same as TC-RPT-109).</t>
-        </is>
-      </c>
-      <c r="D13" s="6" t="inlineStr">
-        <is>
-          <t>SETUP: Via API (as accountant) — close the report month covering yesterday but keep the confirmation period open.
-SETUP: Via API (as manager) — POST approvable task_reports for the employee on yesterday, then POST a reject with `cause = 'regression #3321'`. Wait ≥ 5 min.
-SETUP: Clear historical APPROVE_REJECT emails.
-TRIGGER: `POST /api/ttt/v1/test/reports/notify-rejected`.
-WAIT: 60 s.
-DB-CHECK: `reject.executor_notified = true`.
-EMAIL-CHECK: Employee mailbox receives the APPROVE_REJECT email.
-CLEANUP: Via API — DELETE reject; reopen report month if this test polluted the env's period state.</t>
-        </is>
-      </c>
-      <c r="E13" s="6" t="inlineStr">
-        <is>
-          <t>Regression #3321 — even with the report month closed, the reject notification still dispatches when the confirmation period is open. Pre-fix, executor_notified stayed false and no email arrived.</t>
-        </is>
-      </c>
-      <c r="F13" s="15" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G13" s="15" t="inlineStr">
-        <is>
-          <t>Hybrid</t>
-        </is>
-      </c>
-      <c r="H13" s="6" t="inlineStr">
-        <is>
-          <t>#3423 row 4; #3321 regression</t>
-        </is>
-      </c>
-      <c r="I13" s="6" t="inlineStr">
-        <is>
-          <t>reports/cron/reject</t>
-        </is>
-      </c>
-      <c r="J13" s="6" t="inlineStr">
-        <is>
-          <t>#3321 Frontend+backend interplay — verify both DB flag AND email arrival.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="16" t="inlineStr">
-        <is>
-          <t>TC-RPT-112</t>
-        </is>
-      </c>
-      <c r="B14" s="8" t="inlineStr">
-        <is>
-          <t>Reject notification — idempotency: already-notified reject not re-sent on subsequent runs</t>
-        </is>
-      </c>
-      <c r="C14" s="8" t="inlineStr">
-        <is>
-          <t>Env: ttt-qa-1.
-Pre-state: TC-RPT-109 or TC-RPT-111 ran and set `reject.executor_notified = true`.</t>
-        </is>
-      </c>
-      <c r="D14" s="8" t="inlineStr">
-        <is>
-          <t>SETUP: Confirm pre-state — `SELECT executor_notified FROM ttt_backend.reject WHERE id = &lt;reject_id&gt;` returns `true`; baseline email count for the employee.
-TRIGGER: `POST /api/ttt/v1/test/reports/notify-rejected`.
-WAIT: 60 s.
-DB-CHECK: `executor_notified` stays `true` (unchanged).
-EMAIL-CHECK: Roundcube — email count unchanged (no new APPROVE_REJECT for this reject_id).
-CLEANUP: None.</t>
-        </is>
-      </c>
-      <c r="E14" s="8" t="inlineStr">
-        <is>
-          <t>Rejects filtered by `executor_notified = false` — once true, the query excludes them on every subsequent run.</t>
-        </is>
-      </c>
-      <c r="F14" s="16" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G14" s="16" t="inlineStr">
-        <is>
-          <t>Hybrid</t>
-        </is>
-      </c>
-      <c r="H14" s="8" t="inlineStr">
-        <is>
-          <t>#3423 row 4</t>
-        </is>
-      </c>
-      <c r="I14" s="8" t="inlineStr">
-        <is>
-          <t>reports/cron/reject</t>
-        </is>
-      </c>
-      <c r="J14" s="8" t="inlineStr">
-        <is>
-          <t>Idempotency via DB-flag predicate.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="15" t="inlineStr">
-        <is>
-          <t>TC-RPT-113</t>
-        </is>
-      </c>
-      <c r="B15" s="6" t="inlineStr">
-        <is>
-          <t>Extended-period cleanup — expired extended report period transitions to closed</t>
-        </is>
-      </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>Env: ttt-qa-1 or timemachine.
-An `extended_report_period` row exists with `end_date &lt; now()` and `closed = false`.
-Query: SELECT id, employee_id, start_date, end_date FROM ttt_backend.extended_report_period WHERE closed = false AND end_date &lt; NOW() - INTERVAL '1 minute' LIMIT 1;
-If none exists, SETUP must create one.</t>
-        </is>
-      </c>
-      <c r="D15" s="6" t="inlineStr">
-        <is>
-          <t>SETUP: If no expired extended period exists, create one via accountant UI/API — `POST /api/ttt/v1/extended-report-periods` with `end_date = NOW() - INTERVAL '1 min'` (or set end_date in the past via DB for timemachine envs).
-SETUP: Capture `closed` value before trigger.
-TRIGGER: `POST /api/ttt/v1/test/reports/cleanup-extended`.
-WAIT: 60 s.
-VERIFY LOG: Graylog — `message:"Extended period clean up started"` → `message:"Extended period clean up finished"` pair within 3 min (both debug level).
-DB-CHECK: `SELECT closed FROM ttt_backend.extended_report_period WHERE id = &lt;row_id&gt;` returns `true`.
-DB-CHECK: No error markers — query `message:"Unable to clean up timed out report extended periods"` is empty in the same window.
-CLEANUP: Delete the seeded extended_report_period row if it was created for this test.</t>
-        </is>
-      </c>
-      <c r="E15" s="6" t="inlineStr">
-        <is>
-          <t>Scheduler marks expired extended periods as closed; log markers show start/finish pair; no error marker.</t>
-        </is>
-      </c>
-      <c r="F15" s="15" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="G15" s="15" t="inlineStr">
-        <is>
-          <t>Hybrid</t>
-        </is>
-      </c>
-      <c r="H15" s="6" t="inlineStr">
-        <is>
-          <t>#3423 row 7; #603</t>
-        </is>
-      </c>
-      <c r="I15" s="6" t="inlineStr">
-        <is>
-          <t>reports/cron/extended-cleanup</t>
-        </is>
-      </c>
-      <c r="J15" s="6" t="inlineStr">
-        <is>
-          <t>Happy-path for extended-period scheduler.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="16" t="inlineStr">
-        <is>
-          <t>TC-RPT-114</t>
-        </is>
-      </c>
-      <c r="B16" s="8" t="inlineStr">
-        <is>
-          <t>Extended-period — regression #2289: EXTENDED_PERIOD_REPORT email not sent to office accountants</t>
-        </is>
-      </c>
-      <c r="C16" s="8" t="inlineStr">
-        <is>
-          <t>Env: ttt-qa-1 or timemachine.
-Env has at least one office accountant and at least one main accountant (role distinction is critical).
-Query: SELECT e.login, r.name FROM ttt_backend.employee e JOIN ttt_backend.employee_role er ON er.employee_id = e.id JOIN ttt_backend.role r ON r.id = er.role_id WHERE e.enabled = true AND r.name IN ('ROLE_OFFICE_ACCOUNTANT', 'ROLE_HEAD_ACCOUNTANT', 'ROLE_DEPARTMENT_MANAGER');</t>
-        </is>
-      </c>
-      <c r="D16" s="8" t="inlineStr">
-        <is>
-          <t>SETUP: Reproduce the full EXTENDED_PERIOD_REPORT trigger flow (per #2289 comment by @mpotter):
-  a. Close the report period (distinct from approve period).
-  b. As accountant — reopen the individual report period for a target employee.
-  c. As that employee — report hours on a project.
-  d. As accountant — close the individual report period (or wait 1 hour for auto-close).
-SETUP: Identify office accountant, main accountant, and project manager of the project above.
-SETUP: Clear historical EXTENDED_PERIOD_REPORT emails from ALL three mailboxes (office accountant, main accountant, PM).
-TRIGGER: `POST /api/ttt/v1/test/reports/cleanup-extended` (or wait for scheduler).
-WAIT: 60 s.
-EMAIL-CHECK: Roundcube — MAIN accountant receives EXTENDED_PERIOD_REPORT; PM receives EXTENDED_PERIOD_REPORT; OFFICE accountant does NOT receive it.
-VERIFY LOG: Graylog — extended-cleanup markers fire; `"Sending notification to = "` mentions only main accountant + PM logins, NOT the office accountant login.
-CLEANUP: Revert period state; DELETE seeded task_reports.</t>
-        </is>
-      </c>
-      <c r="E16" s="8" t="inlineStr">
-        <is>
-          <t>Regression #2289 — office accountants must NOT receive EXTENDED_PERIOD_REPORT; only project managers + main accountants do.</t>
-        </is>
-      </c>
-      <c r="F16" s="16" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G16" s="16" t="inlineStr">
-        <is>
-          <t>Hybrid</t>
-        </is>
-      </c>
-      <c r="H16" s="8" t="inlineStr">
-        <is>
-          <t>#3423 row 7; #2289 regression</t>
-        </is>
-      </c>
-      <c r="I16" s="8" t="inlineStr">
-        <is>
-          <t>reports/cron/extended-cleanup</t>
-        </is>
-      </c>
-      <c r="J16" s="8" t="inlineStr">
-        <is>
-          <t>#2289 fix — tighten recipient audience. Setup flow is complex — reference comment thread on ticket.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="15" t="inlineStr">
-        <is>
-          <t>TC-RPT-115</t>
-        </is>
-      </c>
-      <c r="B17" s="6" t="inlineStr">
-        <is>
-          <t>Extended-period cleanup — idempotency: already-closed periods remain untouched</t>
-        </is>
-      </c>
-      <c r="C17" s="6" t="inlineStr">
-        <is>
-          <t>Env: ttt-qa-1.
-Pre-state: TC-RPT-113 already closed the target extended-period row.</t>
-        </is>
-      </c>
-      <c r="D17" s="6" t="inlineStr">
-        <is>
-          <t>SETUP: Confirm `closed = true` in `ttt_backend.extended_report_period WHERE id = &lt;row_id&gt;`; snapshot `updated_at`.
-TRIGGER: `POST /api/ttt/v1/test/reports/cleanup-extended`.
-WAIT: 60 s.
-VERIFY LOG: Graylog — start/finish pair fires, but service should touch 0 rows.
-DB-CHECK: `SELECT updated_at FROM ttt_backend.extended_report_period WHERE id = &lt;row_id&gt;` unchanged from snapshot.
-CLEANUP: None.</t>
-        </is>
-      </c>
-      <c r="E17" s="6" t="inlineStr">
-        <is>
-          <t>Query filter `closed = false` excludes this row; cleanup is a no-op.</t>
-        </is>
-      </c>
-      <c r="F17" s="15" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G17" s="15" t="inlineStr">
-        <is>
-          <t>Hybrid</t>
-        </is>
-      </c>
-      <c r="H17" s="6" t="inlineStr">
-        <is>
-          <t>#3423 row 7</t>
-        </is>
-      </c>
-      <c r="I17" s="6" t="inlineStr">
-        <is>
-          <t>reports/cron/extended-cleanup</t>
-        </is>
-      </c>
-      <c r="J17" s="6" t="inlineStr">
-        <is>
-          <t>Idempotency via closed-flag predicate.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="00F4B084"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:J7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="45" customWidth="1" min="3" max="3"/>
-    <col width="72" customWidth="1" min="4" max="4"/>
-    <col width="45" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="35" customWidth="1" min="8" max="8"/>
-    <col width="26" customWidth="1" min="9" max="9"/>
-    <col width="35" customWidth="1" min="10" max="10"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="4">
-        <f>HYPERLINK("#'Plan Overview'!A1", "← Back to Plan Overview")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="14" t="inlineStr">
-        <is>
-          <t>Test ID</t>
-        </is>
-      </c>
-      <c r="B2" s="14" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
-      <c r="C2" s="14" t="inlineStr">
-        <is>
-          <t>Preconditions</t>
-        </is>
-      </c>
-      <c r="D2" s="14" t="inlineStr">
-        <is>
-          <t>Steps</t>
-        </is>
-      </c>
-      <c r="E2" s="14" t="inlineStr">
-        <is>
-          <t>Expected Result</t>
-        </is>
-      </c>
-      <c r="F2" s="14" t="inlineStr">
-        <is>
-          <t>Priority</t>
-        </is>
-      </c>
-      <c r="G2" s="14" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="H2" s="14" t="inlineStr">
-        <is>
-          <t>Requirement Ref</t>
-        </is>
-      </c>
-      <c r="I2" s="14" t="inlineStr">
-        <is>
-          <t>Module/Component</t>
-        </is>
-      </c>
-      <c r="J2" s="14" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="15" t="inlineStr">
-        <is>
-          <t>TC-RPT-116</t>
-        </is>
-      </c>
-      <c r="B3" s="6" t="inlineStr">
-        <is>
-          <t>Budget notification — EXCEEDED: first crossing of budget_limit dispatches BUDGET_NOTIFICATION_EXCEEDED</t>
-        </is>
-      </c>
-      <c r="C3" s="6" t="inlineStr">
-        <is>
-          <t>Env: ttt-qa-1.
-A `BudgetNotification` entity seeded for a (project, employee, date range) with budget_limit = 4 hours. Target employee has NOT yet reported hours in the window.
-Query to pick a project+employee: SELECT p.id, p.name, e.login FROM ttt_backend.project p JOIN ttt_backend.employee_project ep ON ep.project_id = p.id JOIN ttt_backend.employee e ON e.id = ep.employee_id WHERE p.status = 'ACTIVE' AND e.enabled = true AND e.login &lt;&gt; 'pvaynmaster' ORDER BY random() LIMIT 1;</t>
-        </is>
-      </c>
-      <c r="D3" s="6" t="inlineStr">
-        <is>
-          <t>SETUP: Pick an active (project, employee, manager-watcher) triple.
-SETUP: Via API — `POST /api/ttt/v1/budget-notifications` with watcher_id = &lt;mgr_id&gt;, project_id = &lt;project_id&gt;, employee_id = &lt;emp_id&gt;, budget_limit = 240 (4 hours in minutes), start_date = today, end_date = today.
-SETUP: Clear historical BUDGET_NOTIFICATION_EXCEEDED emails from watcher's mailbox.
-STEP (UI): Login as the employee; navigate to My Tasks; report 5 hours on a task of &lt;project_id&gt; for today.
-STEP: Wait ≥ 10 s (SAFETY_INTERVAL_SECONDS) so the task_report is considered stable.
-TRIGGER: `POST /api/ttt/v1/test/budgets/notify`.
-WAIT: 30 s (scheduler cadence + email-send cadence).
-VERIFY LOG: Graylog — `message:"Budget notification job is done"` fires (info).
-DB-CHECK: `SELECT limit_reached_date FROM ttt_backend.budget_notification WHERE id = &lt;notif_id&gt;` is non-null and equals today.
-EMAIL-CHECK: Roundcube — watcher mailbox receives email whose template key maps to `BUDGET_NOTIFICATION_EXCEEDED`.
-CLEANUP: Via API — DELETE the seeded BudgetNotification and the task_report.</t>
-        </is>
-      </c>
-      <c r="E3" s="6" t="inlineStr">
-        <is>
-          <t>First budget crossing — BudgetServiceImpl detects prev=null → current=today transition; dispatches EXCEEDED template to watcher.</t>
-        </is>
-      </c>
-      <c r="F3" s="15" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="G3" s="15" t="inlineStr">
-        <is>
-          <t>Hybrid</t>
-        </is>
-      </c>
-      <c r="H3" s="6" t="inlineStr">
-        <is>
-          <t>#3423 row 5; delta #3 (three templates); #892 regression</t>
-        </is>
-      </c>
-      <c r="I3" s="6" t="inlineStr">
-        <is>
-          <t>reports/cron/budget</t>
-        </is>
-      </c>
-      <c r="J3" s="6" t="inlineStr">
-        <is>
-          <t>Delta #3 folded — template is BUDGET_NOTIFICATION_EXCEEDED. SAFETY_INTERVAL_SECONDS=10 means recent task_reports are skipped.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="16" t="inlineStr">
-        <is>
-          <t>TC-RPT-117</t>
-        </is>
-      </c>
-      <c r="B4" s="8" t="inlineStr">
-        <is>
-          <t>Budget notification — NOT_REACHED: exceeded budget then reduced dispatches BUDGET_NOTIFICATION_NOT_REACHED</t>
-        </is>
-      </c>
-      <c r="C4" s="8" t="inlineStr">
-        <is>
-          <t>Env: ttt-qa-1.
-Pre-state: TC-RPT-116 dispatched EXCEEDED; `limit_reached_date = today`.</t>
-        </is>
-      </c>
-      <c r="D4" s="8" t="inlineStr">
-        <is>
-          <t>SETUP: Confirm pre-state — `limit_reached_date` non-null for &lt;notif_id&gt;.
-STEP (UI): Login as the employee; navigate to My Tasks; edit the 5h entry down to 2h for today.
-STEP: Wait ≥ 10 s.
-TRIGGER: `POST /api/ttt/v1/test/budgets/notify`.
-WAIT: 30 s.
-DB-CHECK: `limit_reached_date` now `null` (prev=today → current=null transition).
-EMAIL-CHECK: Watcher mailbox receives email matching BUDGET_NOTIFICATION_NOT_REACHED.
-VERIFY LOG: `"Budget notification job is done"` fires.
-CLEANUP: Delete seeded entities.</t>
-        </is>
-      </c>
-      <c r="E4" s="8" t="inlineStr">
-        <is>
-          <t>Budget fell below limit — NOT_REACHED template dispatched. limit_reached_date cleared back to null.</t>
-        </is>
-      </c>
-      <c r="F4" s="16" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G4" s="16" t="inlineStr">
-        <is>
-          <t>Hybrid</t>
-        </is>
-      </c>
-      <c r="H4" s="8" t="inlineStr">
-        <is>
-          <t>#3423 row 5; delta #3; #892 regression</t>
-        </is>
-      </c>
-      <c r="I4" s="8" t="inlineStr">
-        <is>
-          <t>reports/cron/budget</t>
-        </is>
-      </c>
-      <c r="J4" s="8" t="inlineStr">
-        <is>
-          <t>Template key BUDGET_NOTIFICATION_NOT_REACHED.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="15" t="inlineStr">
-        <is>
-          <t>TC-RPT-118</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>Budget notification — DATE_UPDATED: hours moved to a different day keeping budget exceeded</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="inlineStr">
-        <is>
-          <t>Env: ttt-qa-1.
-Pre-state: TC-RPT-116 dispatched EXCEEDED for today's report.</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>SETUP: Confirm `limit_reached_date = today` in DB.
-STEP (UI): Login as employee; move today's 5h entry to yesterday (delete today's report, create an identical one for yesterday with 5h).
-SETUP: Via API (if UI does not allow yesterday edit) — DELETE today's task_report; POST the same hours on yesterday.
-STEP: Wait ≥ 10 s.
-TRIGGER: `POST /api/ttt/v1/test/budgets/notify`.
-WAIT: 30 s.
-DB-CHECK: `limit_reached_date` changed from today → yesterday.
-EMAIL-CHECK: Watcher receives email matching BUDGET_NOTIFICATION_DATE_UPDATED.
-CLEANUP: Delete seeded entities.</t>
-        </is>
-      </c>
-      <c r="E5" s="6" t="inlineStr">
-        <is>
-          <t>Budget still exceeded but on a different date — DATE_UPDATED template dispatched.</t>
-        </is>
-      </c>
-      <c r="F5" s="15" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G5" s="15" t="inlineStr">
-        <is>
-          <t>Hybrid</t>
-        </is>
-      </c>
-      <c r="H5" s="6" t="inlineStr">
-        <is>
-          <t>#3423 row 5; delta #3; #892 regression</t>
-        </is>
-      </c>
-      <c r="I5" s="6" t="inlineStr">
-        <is>
-          <t>reports/cron/budget</t>
-        </is>
-      </c>
-      <c r="J5" s="6" t="inlineStr">
-        <is>
-          <t>Template key BUDGET_NOTIFICATION_DATE_UPDATED.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="16" t="inlineStr">
-        <is>
-          <t>TC-RPT-119</t>
-        </is>
-      </c>
-      <c r="B6" s="8" t="inlineStr">
-        <is>
-          <t>Budget notification — safety window: task_report younger than 10 s is skipped by next run</t>
-        </is>
-      </c>
-      <c r="C6" s="8" t="inlineStr">
-        <is>
-          <t>Env: ttt-qa-1.
-Seeded BudgetNotification (same shape as TC-RPT-116).</t>
-        </is>
-      </c>
-      <c r="D6" s="8" t="inlineStr">
-        <is>
-          <t>SETUP: Seed BudgetNotification as in TC-RPT-116; confirm `limit_reached_date = null`.
-STEP (UI): Report 5h on the project for today.
-TRIGGER: `POST /api/ttt/v1/test/budgets/notify` within 5 s of the report (definitely &lt; SAFETY_INTERVAL_SECONDS=10).
-WAIT: 30 s.
-DB-CHECK: `limit_reached_date` still `null` (skipped — too recent).
-EMAIL-CHECK: No BUDGET_NOTIFICATION_EXCEEDED email yet.
-WAIT: additional 15 s (total ~20 s past the report).
-TRIGGER 2: `POST /api/ttt/v1/test/budgets/notify`.
-WAIT: 30 s.
-DB-CHECK: `limit_reached_date = today` now.
-EMAIL-CHECK: Email arrives.
-CLEANUP: Delete seeded entities.</t>
-        </is>
-      </c>
-      <c r="E6" s="8" t="inlineStr">
-        <is>
-          <t>SAFETY_INTERVAL_SECONDS=10 guards against flapping; first trigger skips, second trigger (after safety window) dispatches.</t>
-        </is>
-      </c>
-      <c r="F6" s="16" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G6" s="16" t="inlineStr">
-        <is>
-          <t>Hybrid</t>
-        </is>
-      </c>
-      <c r="H6" s="8" t="inlineStr">
-        <is>
-          <t>#3423 row 5; delta #3 (SAFETY_INTERVAL_SECONDS=10)</t>
-        </is>
-      </c>
-      <c r="I6" s="8" t="inlineStr">
-        <is>
-          <t>reports/cron/budget</t>
-        </is>
-      </c>
-      <c r="J6" s="8" t="inlineStr">
-        <is>
-          <t>Timing-sensitive. Real-time env; cannot advance clock easily here.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="15" t="inlineStr">
-        <is>
-          <t>TC-RPT-120</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>Budget notification — recipient: email goes to watcher_id, not employee</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>Env: ttt-qa-1.
-Seeded BudgetNotification with watcher_id = &lt;mgr_id&gt;, employee_id = &lt;emp_id&gt;, and mgr_id ≠ emp_id.</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>SETUP: Seed as in TC-RPT-116 with distinct watcher and employee.
-SETUP: Clear BUDGET_NOTIFICATION_EXCEEDED emails from BOTH mailboxes.
-STEP (UI): Employee reports 5h for today on the project.
-STEP: Wait 15 s (past SAFETY_INTERVAL).
-TRIGGER: `POST /api/ttt/v1/test/budgets/notify`.
-WAIT: 30 s.
-EMAIL-CHECK: Watcher's mailbox has ONE new EXCEEDED email; employee's mailbox has ZERO new BUDGET_* emails.
-VERIFY LOG: `"Budget notification job is done"` fires.
-CLEANUP: Delete seeded entities.</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>Email sent only to `notification.watcherId` resolved via employeeService.find(watcherId); employee never receives a copy.</t>
-        </is>
-      </c>
-      <c r="F7" s="15" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G7" s="15" t="inlineStr">
-        <is>
-          <t>Hybrid</t>
-        </is>
-      </c>
-      <c r="H7" s="6" t="inlineStr">
-        <is>
-          <t>#3423 row 5</t>
-        </is>
-      </c>
-      <c r="I7" s="6" t="inlineStr">
-        <is>
-          <t>reports/cron/budget</t>
-        </is>
-      </c>
-      <c r="J7" s="6" t="inlineStr">
-        <is>
-          <t>Recipient-correctness guard.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
